--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16462.07</v>
+        <v>16403.46</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9697.860000000001</v>
+        <v>9663.33</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5541.52</v>
+        <v>5521.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3202.27</v>
+        <v>3190.87</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2214.84</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1696.3</v>
+        <v>1690.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2268.95</v>
+        <v>2260.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1904.02</v>
+        <v>1897.24</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1434.04</v>
+        <v>1428.94</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1024.27</v>
+        <v>1020.62</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1398.6</v>
+        <v>1393.62</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>883.23</v>
+        <v>880.09</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1437.01</v>
+        <v>1431.89</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1331.35</v>
+        <v>1326.61</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1693.29</v>
+        <v>1687.27</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2359.42</v>
+        <v>2351.02</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1562.26</v>
+        <v>1556.7</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15571.08</v>
+        <v>15515.64</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4362.31</v>
+        <v>4346.78</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4042.25</v>
+        <v>4027.86</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2124.11</v>
+        <v>2116.55</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5573.67</v>
+        <v>5553.82</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3819.75</v>
+        <v>3806.15</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1592.07</v>
+        <v>1586.4</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>829.01</v>
+        <v>826.0599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>912.29</v>
+        <v>909.05</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10225.2</v>
+        <v>10188.8</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4133.84</v>
+        <v>4119.12</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4468.58</v>
+        <v>4452.67</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2779.12</v>
+        <v>2769.23</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1818.92</v>
+        <v>1812.44</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1474.44</v>
+        <v>1469.19</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2177.81</v>
+        <v>2170.06</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2161.42</v>
+        <v>2153.73</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>832.87</v>
+        <v>829.9</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>811.08</v>
+        <v>808.1900000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2810.29</v>
+        <v>2800.28</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3010.05</v>
+        <v>2999.34</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1998.45</v>
+        <v>1991.34</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4174.26</v>
+        <v>4159.4</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2571.29</v>
+        <v>2552.05</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2022.26</v>
+        <v>2007.13</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>826.84</v>
+        <v>820.65</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2264.9</v>
+        <v>2247.95</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1205.12</v>
+        <v>1196.1</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>809.73</v>
+        <v>803.67</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>839.34</v>
+        <v>833.0599999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>852.3099999999999</v>
+        <v>845.9299999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1483.75</v>
+        <v>1472.65</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1130.58</v>
+        <v>1122.11</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12335.02</v>
+        <v>12242.71</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3507.14</v>
+        <v>3480.89</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1058.58</v>
+        <v>1050.66</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>812.83</v>
+        <v>806.74</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>923.85</v>
+        <v>916.9299999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4467.49</v>
+        <v>4434.06</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4786.06</v>
+        <v>4750.24</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>822.5599999999999</v>
+        <v>816.4</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>878.87</v>
+        <v>872.29</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2944.81</v>
+        <v>2922.78</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8673.549999999999</v>
+        <v>8608.629999999999</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2700.53</v>
+        <v>2680.32</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5896.23</v>
+        <v>5852.1</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1732.56</v>
+        <v>1719.59</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2225.96</v>
+        <v>2209.3</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4361.62</v>
+        <v>4328.98</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1486.96</v>
+        <v>1475.83</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10173.68</v>
+        <v>10097.54</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1130.57</v>
+        <v>1122.11</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4659.43</v>
+        <v>4624.56</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4462.4</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1569.59</v>
+        <v>1557.84</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1294.5</v>
+        <v>1284.81</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>914.17</v>
+        <v>907.33</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>835.28</v>
+        <v>829.03</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9991.9</v>
+        <v>9917.120000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1743.14</v>
+        <v>1730.1</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3017.67</v>
+        <v>2995.09</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>897.6799999999999</v>
+        <v>890.96</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1136.78</v>
+        <v>1128.27</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4862.48</v>
+        <v>4826.09</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1346.13</v>
+        <v>1336.06</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2779.67</v>
+        <v>2758.86</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8568.629999999999</v>
+        <v>8504.5</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>812.89</v>
+        <v>806.8099999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4728.48</v>
+        <v>4693.1</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>9948.42</v>
+        <v>9977.24</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1525.2</v>
+        <v>1529.62</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1121.02</v>
+        <v>1124.27</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2487.97</v>
+        <v>2495.17</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5694.26</v>
+        <v>5710.76</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>9667.690000000001</v>
+        <v>9695.700000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1433.16</v>
+        <v>1437.31</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1909.62</v>
+        <v>1915.15</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2367.11</v>
+        <v>2373.96</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1771.34</v>
+        <v>1776.48</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4627.11</v>
+        <v>4640.51</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1316.42</v>
+        <v>1320.24</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1075.25</v>
+        <v>1078.37</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2938.65</v>
+        <v>2947.17</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2150.51</v>
+        <v>2156.74</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3625.87</v>
+        <v>3636.37</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2674.19</v>
+        <v>2681.94</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>13478.76</v>
+        <v>13517.8</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4626.65</v>
+        <v>4640.05</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9277.280000000001</v>
+        <v>9304.16</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1913.14</v>
+        <v>1918.68</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1241.81</v>
+        <v>1245.41</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6226.86</v>
+        <v>6244.9</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4214.07</v>
+        <v>4226.28</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3339.64</v>
+        <v>3349.32</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1494.97</v>
+        <v>1499.3</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>817.8</v>
+        <v>820.16</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>811.41</v>
+        <v>813.77</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1820.99</v>
+        <v>1826.26</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3981.3</v>
+        <v>3992.83</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3071.04</v>
+        <v>3079.94</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1127.68</v>
+        <v>1130.94</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6960.45</v>
+        <v>6980.62</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1738.07</v>
+        <v>1743.1</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>32072.56</v>
+        <v>32165.47</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2703.42</v>
+        <v>2711.25</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3079.03</v>
+        <v>3087.95</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2802.1</v>
+        <v>2810.21</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>858.03</v>
+        <v>860.51</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4320.47</v>
+        <v>4332.98</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>39985.54</v>
+        <v>40101.38</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2139.37</v>
+        <v>2145.57</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>4291.22</v>
+        <v>4303.65</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1948.52</v>
+        <v>1954.16</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1031.91</v>
+        <v>1034.9</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1572.02</v>
+        <v>1576.58</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5488.25</v>
+        <v>5504.15</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1432.94</v>
+        <v>1440.34</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1304.28</v>
+        <v>1311.01</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>17399.92</v>
+        <v>17489.8</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3952.91</v>
+        <v>3973.33</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1274.49</v>
+        <v>1281.07</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>819.1799999999999</v>
+        <v>823.41</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2082.52</v>
+        <v>2093.27</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2282.07</v>
+        <v>2293.86</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1019.83</v>
+        <v>1025.1</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4873.09</v>
+        <v>4898.26</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2173.69</v>
+        <v>2184.92</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>29168.32</v>
+        <v>29318.99</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1561.69</v>
+        <v>1569.76</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>12184.66</v>
+        <v>12247.6</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1635.9</v>
+        <v>1644.35</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>7016.14</v>
+        <v>7052.38</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2842.44</v>
+        <v>2857.12</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1291.43</v>
+        <v>1298.1</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>10822.94</v>
+        <v>10878.84</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>816.97</v>
+        <v>821.1900000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>28998.64</v>
+        <v>29148.44</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2204.91</v>
+        <v>2216.3</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5053.47</v>
+        <v>5079.58</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1252.95</v>
+        <v>1259.42</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6056.87</v>
+        <v>6088.16</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3114.77</v>
+        <v>3130.86</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1744.92</v>
+        <v>1753.94</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9775.719999999999</v>
+        <v>9826.219999999999</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1451.71</v>
+        <v>1459.21</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2371.39</v>
+        <v>2383.64</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>899.83</v>
+        <v>904.48</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3118.89</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3716.48</v>
+        <v>3735.68</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>30420.35</v>
+        <v>30577.49</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>9904.66</v>
+        <v>9955.83</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>4622.04</v>
+        <v>4645.91</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>52723.32</v>
+        <v>52995.67</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2628.89</v>
+        <v>2617.81</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1130.32</v>
+        <v>1125.56</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1627.53</v>
+        <v>1620.67</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2846.25</v>
+        <v>2834.24</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2213.14</v>
+        <v>2203.81</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5867.03</v>
+        <v>5842.3</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1072.54</v>
+        <v>1068.02</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>946.8099999999999</v>
+        <v>942.8200000000001</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2988.26</v>
+        <v>2975.66</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>9399.459999999999</v>
+        <v>9359.82</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7006.11</v>
+        <v>6976.57</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>10328.74</v>
+        <v>10285.19</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2222.71</v>
+        <v>2213.34</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1499.39</v>
+        <v>1493.07</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>886.96</v>
+        <v>883.22</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1559.49</v>
+        <v>1552.91</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4925.97</v>
+        <v>4905.21</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1445.94</v>
+        <v>1439.84</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2505.57</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3295.81</v>
+        <v>3281.91</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5314.84</v>
+        <v>5292.43</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6329.1</v>
+        <v>6302.42</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>14076.32</v>
+        <v>14016.97</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1176.21</v>
+        <v>1171.25</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4904.57</v>
+        <v>4883.89</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>6502.32</v>
+        <v>6474.9</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1902.3</v>
+        <v>1894.28</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1591.97</v>
+        <v>1596.34</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11039.68</v>
+        <v>11069.98</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1160.68</v>
+        <v>1163.87</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2128.49</v>
+        <v>2134.33</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3281.67</v>
+        <v>3290.68</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>870.8099999999999</v>
+        <v>873.2</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3348.5</v>
+        <v>3357.69</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4684</v>
+        <v>4696.86</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1952.89</v>
+        <v>1958.25</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1525.01</v>
+        <v>1529.2</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>813.83</v>
+        <v>816.0599999999999</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>817.52</v>
+        <v>819.76</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>65163.65</v>
+        <v>65342.54</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1541.12</v>
+        <v>1545.36</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1158.45</v>
+        <v>1161.63</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1997.39</v>
+        <v>2002.88</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4320.58</v>
+        <v>4332.44</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>889.97</v>
+        <v>892.41</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4596.63</v>
+        <v>4609.25</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3636.34</v>
+        <v>3646.32</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1204.93</v>
+        <v>1208.24</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1080.31</v>
+        <v>1083.28</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>833.21</v>
+        <v>835.49</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>4179.82</v>
+        <v>4191.29</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1021.42</v>
+        <v>1024.22</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4246.75</v>
+        <v>4258.41</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1234.95</v>
+        <v>1238.34</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1549.88</v>
+        <v>1554.14</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>50063.82</v>
+        <v>50201.26</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>937.3200000000001</v>
+        <v>939.89</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1492.02</v>
+        <v>1505.59</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1911.41</v>
+        <v>1928.8</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2206.91</v>
+        <v>2226.98</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2461.73</v>
+        <v>2484.13</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>912.77</v>
+        <v>921.0700000000001</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>818.5</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>10214.8</v>
+        <v>10307.71</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>21974.89</v>
+        <v>22174.77</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>27187.02</v>
+        <v>27434.31</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3740.68</v>
+        <v>3774.71</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2105.92</v>
+        <v>2125.07</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1192.98</v>
+        <v>1203.83</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2320.63</v>
+        <v>2341.73</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2509.43</v>
+        <v>2532.26</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3495.37</v>
+        <v>3527.16</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1447.02</v>
+        <v>1460.18</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1708.95</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1439.47</v>
+        <v>1452.56</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5635.79</v>
+        <v>5687.05</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1835.76</v>
+        <v>1852.46</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>5713.66</v>
+        <v>5765.63</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1255.13</v>
+        <v>1266.55</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>3719.28</v>
+        <v>3753.11</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>4682.43</v>
+        <v>4725.02</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>876.77</v>
+        <v>884.75</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1877.45</v>
+        <v>1894.53</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>8433.85</v>
+        <v>8510.57</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2574.33</v>
+        <v>2597.75</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1419.49</v>
+        <v>1432.4</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1613.01</v>
+        <v>1627.69</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6142.14</v>
+        <v>6198.01</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>9094.48</v>
+        <v>9177.200000000001</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>878.4</v>
+        <v>886.39</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>828.42</v>
+        <v>835.95</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1294.23</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1481.35</v>
+        <v>1494.83</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>9769.65</v>
+        <v>9858.51</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>13477.36</v>
+        <v>13599.95</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3677.6</v>
+        <v>3711.05</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1078.22</v>
+        <v>1088.03</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>6285.59</v>
+        <v>6342.77</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1496.03</v>
+        <v>1509.64</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>8154.07</v>
+        <v>8228.24</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2955.27</v>
+        <v>2982.15</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3441.78</v>
+        <v>3473.08</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2514.13</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1904.08</v>
+        <v>1921.4</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>994.37</v>
+        <v>1003.41</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>5744.7</v>
+        <v>5796.95</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4764.4</v>
+        <v>4807.74</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>809.98</v>
+        <v>815.62</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6799.62</v>
+        <v>6846.96</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3775.18</v>
+        <v>3801.46</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1306.71</v>
+        <v>1315.8</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>823.37</v>
+        <v>829.1</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4812</v>
+        <v>4845.5</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>8057.3</v>
+        <v>8113.4</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1137.56</v>
+        <v>1145.48</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>9988.450000000001</v>
+        <v>10057.99</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>44818.83</v>
+        <v>45130.86</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2904.23</v>
+        <v>2924.45</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3618.18</v>
+        <v>3643.37</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>982.11</v>
+        <v>988.95</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4585.99</v>
+        <v>4617.92</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1250.13</v>
+        <v>1258.83</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1232.59</v>
+        <v>1241.17</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>812.21</v>
+        <v>817.87</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2378.88</v>
+        <v>2395.44</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2537.21</v>
+        <v>2554.87</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5171.82</v>
+        <v>5207.83</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>833.95</v>
+        <v>839.75</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1435.26</v>
+        <v>1445.25</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5630.93</v>
+        <v>5670.13</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>5605.71</v>
+        <v>5644.74</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1705.81</v>
+        <v>1717.69</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>5432.18</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>24765.78</v>
+        <v>24938.21</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>9897.120000000001</v>
+        <v>9966.02</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1036.7</v>
+        <v>1043.91</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>5915.13</v>
+        <v>5956.31</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>18886.05</v>
+        <v>19017.54</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>9465.68</v>
+        <v>9531.59</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>843.6</v>
+        <v>849.47</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1045.35</v>
+        <v>1052.63</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3749.1</v>
+        <v>3775.21</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>821.8</v>
+        <v>827.52</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>15378.12</v>
+        <v>15485.18</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1318.95</v>
+        <v>1328.13</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>10009.96</v>
+        <v>10079.65</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1162.72</v>
+        <v>1170.82</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1412.97</v>
+        <v>1422.81</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>894.2</v>
+        <v>900.09</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>6987.44</v>
+        <v>7033.45</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1169.03</v>
+        <v>1176.72</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5758.73</v>
+        <v>5796.66</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2308.02</v>
+        <v>2323.22</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>821.41</v>
+        <v>826.8200000000001</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1255.36</v>
+        <v>1263.63</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4433.28</v>
+        <v>4462.47</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1322.49</v>
+        <v>1331.2</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>823.88</v>
+        <v>829.3099999999999</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1919.42</v>
+        <v>1932.06</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>811.67</v>
+        <v>817.02</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1717.6</v>
+        <v>1728.91</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>5374.89</v>
+        <v>5410.29</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2317.74</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3491.73</v>
+        <v>3514.73</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1286.48</v>
+        <v>1294.96</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>893.05</v>
+        <v>898.9299999999999</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2128.89</v>
+        <v>2142.91</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1611.96</v>
+        <v>1622.57</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>6059.2</v>
+        <v>6099.1</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3612.89</v>
+        <v>3636.68</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>4123.3</v>
+        <v>4150.45</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1239.26</v>
+        <v>1247.42</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1520.04</v>
+        <v>1530.06</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>4932.45</v>
+        <v>4964.93</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>1122.88</v>
+        <v>1130.28</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>10163.47</v>
+        <v>10230.4</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1990.33</v>
+        <v>2003.44</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>871.9400000000001</v>
+        <v>877.6799999999999</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>3327.75</v>
+        <v>3349.66</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2210.54</v>
+        <v>2225.09</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1523.8</v>
+        <v>1533.84</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1155.73</v>
+        <v>1163.34</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1163.45</v>
+        <v>1171.12</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1759.55</v>
+        <v>1771.14</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>832.73</v>
+        <v>838.22</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>8895.690000000001</v>
+        <v>8954.280000000001</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2482.52</v>
+        <v>2498.87</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1003.46</v>
+        <v>1010.07</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1029.38</v>
+        <v>1036.16</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1877.92</v>
+        <v>1890.29</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1482.26</v>
+        <v>1492.02</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4674.91</v>
+        <v>4705.7</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>3369.78</v>
+        <v>3391.97</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3986.76</v>
+        <v>4013.01</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2561.35</v>
+        <v>2578.22</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6178.55</v>
+        <v>6233.58</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2301.98</v>
+        <v>2322.48</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>11595.36</v>
+        <v>11698.63</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3610.43</v>
+        <v>3642.59</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>7894.48</v>
+        <v>7964.79</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2722.25</v>
+        <v>2746.49</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1860.16</v>
+        <v>1876.73</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>5234.65</v>
+        <v>5281.27</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2522.41</v>
+        <v>2544.88</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1336.99</v>
+        <v>1348.9</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>11594.11</v>
+        <v>11697.38</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1871.93</v>
+        <v>1888.6</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>3116.02</v>
+        <v>3143.77</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>9672.059999999999</v>
+        <v>9758.209999999999</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4095.19</v>
+        <v>4131.66</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3555.71</v>
+        <v>3587.38</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>6118.82</v>
+        <v>6173.32</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>11831.5</v>
+        <v>11936.88</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>7015.87</v>
+        <v>7078.36</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>834.02</v>
+        <v>841.4400000000001</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>885.89</v>
+        <v>893.78</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1325.92</v>
+        <v>1337.72</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1737.99</v>
+        <v>1753.47</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>944.65</v>
+        <v>953.0599999999999</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>938.73</v>
+        <v>947.09</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>966.33</v>
+        <v>974.9400000000001</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1232.08</v>
+        <v>1243.05</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>2897.97</v>
+        <v>2923.78</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2162.11</v>
+        <v>2181.36</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2699.89</v>
+        <v>2723.94</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1420.32</v>
+        <v>1432.97</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>4507.54</v>
+        <v>4547.69</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>831.85</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3962.46</v>
+        <v>3997.75</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1242.94</v>
+        <v>1254.01</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>5398.95</v>
+        <v>5447.03</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>4150.86</v>
+        <v>4187.83</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>1373.37</v>
+        <v>1385.61</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>3850.71</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>21980.1</v>
+        <v>22175.87</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3361.74</v>
+        <v>3391.68</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3748.57</v>
+        <v>3781.96</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3797.79</v>
+        <v>3831.61</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1241.62</v>
+        <v>1252.67</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2310.85</v>
+        <v>2331.43</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2699.94</v>
+        <v>2723.99</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1681.54</v>
+        <v>1696.51</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>940.5599999999999</v>
+        <v>948.9400000000001</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>993.9400000000001</v>
+        <v>1002.8</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2955.74</v>
+        <v>2982.07</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>3846.35</v>
+        <v>3839.75</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>1197.13</v>
+        <v>1195.08</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>2368.21</v>
+        <v>2364.15</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2693.27</v>
+        <v>2688.65</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1669.14</v>
+        <v>1666.28</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>4224.54</v>
+        <v>4217.3</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>1561.32</v>
+        <v>1558.65</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>16818.11</v>
+        <v>16789.28</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1019.48</v>
+        <v>1017.73</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>24584.03</v>
+        <v>24541.9</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>30212.46</v>
+        <v>30160.68</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>15840.61</v>
+        <v>15813.46</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>2670.18</v>
+        <v>2665.6</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>812.58</v>
+        <v>811.1900000000001</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1025.37</v>
+        <v>1023.61</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>36817.14</v>
+        <v>36754.03</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>4422.85</v>
+        <v>4415.27</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>846.11</v>
+        <v>844.66</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>8235.870000000001</v>
+        <v>8221.76</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>64149.28</v>
+        <v>64039.33</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1083.13</v>
+        <v>1081.27</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1081.58</v>
+        <v>1079.73</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3164.92</v>
+        <v>3159.5</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>2109.65</v>
+        <v>2106.03</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>5760.87</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>2584.16</v>
+        <v>2579.73</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>878.26</v>
+        <v>876.76</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1991.75</v>
+        <v>1988.34</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>10825.44</v>
+        <v>10806.88</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>8365.73</v>
+        <v>8351.389999999999</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>1774.87</v>
+        <v>1773.04</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2939.81</v>
+        <v>2936.78</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>840.64</v>
+        <v>839.78</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>26786.8</v>
+        <v>26759.18</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2417.38</v>
+        <v>2414.89</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2233.06</v>
+        <v>2230.76</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>815.51</v>
+        <v>814.67</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>6365.85</v>
+        <v>6359.29</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>1196.02</v>
+        <v>1194.79</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1522.46</v>
+        <v>1520.89</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2343.03</v>
+        <v>2340.61</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2998.83</v>
+        <v>2995.73</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>955.03</v>
+        <v>954.04</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3000.47</v>
+        <v>2997.38</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>928.51</v>
+        <v>927.55</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1563.9</v>
+        <v>1562.29</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>880.75</v>
+        <v>879.84</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>914.4299999999999</v>
+        <v>913.49</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2985.86</v>
+        <v>2982.78</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>3178.83</v>
+        <v>3175.55</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4364.87</v>
+        <v>4360.37</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>935.46</v>
+        <v>934.5</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>4879.78</v>
+        <v>4874.75</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2642.88</v>
+        <v>2640.16</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>976.28</v>
+        <v>975.27</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1234.37</v>
+        <v>1233.1</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>39908.86</v>
+        <v>39867.7</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>3337.03</v>
+        <v>3333.59</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>938.73</v>
+        <v>937.76</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1453.08</v>
+        <v>1451.58</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>981.67</v>
+        <v>980.65</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>833.01</v>
+        <v>832.15</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>811.38</v>
+        <v>810.54</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1217.58</v>
+        <v>1208.86</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>3342.76</v>
+        <v>3318.81</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>846.51</v>
+        <v>840.45</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>9877.18</v>
+        <v>9806.43</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>1046.89</v>
+        <v>1039.39</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>8149.57</v>
+        <v>8091.19</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>17109.37</v>
+        <v>16986.8</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>2386.53</v>
+        <v>2369.44</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2277.58</v>
+        <v>2261.27</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>44971.15</v>
+        <v>44648.99</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>812.25</v>
+        <v>806.4299999999999</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>8119.65</v>
+        <v>8061.48</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>821.33</v>
+        <v>815.45</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1599.53</v>
+        <v>1588.08</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6755.65</v>
+        <v>6707.25</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>870.76</v>
+        <v>864.52</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>23197.35</v>
+        <v>23031.17</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1608.67</v>
+        <v>1597.15</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>933.27</v>
+        <v>926.58</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>5153.82</v>
+        <v>5116.9</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>10833.3</v>
+        <v>10755.7</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1949.94</v>
+        <v>1935.97</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>25456.75</v>
+        <v>25274.38</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>8258.82</v>
+        <v>8199.66</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1280.7</v>
+        <v>1271.52</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1053.27</v>
+        <v>1045.73</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>5026.96</v>
+        <v>5019.56</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>12867</v>
+        <v>12848.07</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>915.4400000000001</v>
+        <v>914.1</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>848.72</v>
+        <v>847.47</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>3925.49</v>
+        <v>3919.71</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>854.75</v>
+        <v>853.49</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>980.14</v>
+        <v>978.7</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>8494.940000000001</v>
+        <v>8482.440000000001</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1149.25</v>
+        <v>1147.55</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2576.15</v>
+        <v>2572.36</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>29098.9</v>
+        <v>29056.09</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>1980.63</v>
+        <v>1977.71</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>1015</v>
+        <v>1013.5</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>809.66</v>
+        <v>808.47</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1617.85</v>
+        <v>1615.47</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>6071.59</v>
+        <v>6062.66</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>4535.75</v>
+        <v>4529.08</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>5018.04</v>
+        <v>5010.66</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>815.13</v>
+        <v>813.9299999999999</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2095.47</v>
+        <v>2092.38</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>840.96</v>
+        <v>839.72</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>10792.18</v>
+        <v>10776.3</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1037.84</v>
+        <v>1036.31</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>3311.77</v>
+        <v>3306.9</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2743.31</v>
+        <v>2739.28</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>2023.7</v>
+        <v>2020.72</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2544.22</v>
+        <v>2540.48</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3750.76</v>
+        <v>3745.24</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>27743.53</v>
+        <v>27702.71</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>867.29</v>
+        <v>866.01</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2563.09</v>
+        <v>2559.32</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>3336.34</v>
+        <v>3331.43</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>9547.209999999999</v>
+        <v>9533.16</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>3401.27</v>
+        <v>3396.27</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>16095.69</v>
+        <v>16072.01</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2500.98</v>
+        <v>2497.3</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2120</v>
+        <v>2108.46</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>6768.07</v>
+        <v>6731.21</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>3518.01</v>
+        <v>3498.85</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>6041.82</v>
+        <v>6008.91</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1777.78</v>
+        <v>1768.1</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3852.03</v>
+        <v>3831.05</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2273.03</v>
+        <v>2260.65</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>4673.47</v>
+        <v>4648.02</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>811.5700000000001</v>
+        <v>807.15</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>5241.37</v>
+        <v>5212.83</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2348.08</v>
+        <v>2335.3</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>1316.15</v>
+        <v>1308.98</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>815.35</v>
+        <v>810.91</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>912.36</v>
+        <v>907.39</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2567.99</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1052.16</v>
+        <v>1046.43</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1771.93</v>
+        <v>1762.28</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1452.16</v>
+        <v>1444.25</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>13032.69</v>
+        <v>12961.72</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>868.05</v>
+        <v>863.3200000000001</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>7147.98</v>
+        <v>7109.05</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>823.71</v>
+        <v>819.22</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2437.92</v>
+        <v>2424.65</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1916.26</v>
+        <v>1905.83</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2488.59</v>
+        <v>2475.04</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>2380.76</v>
+        <v>2367.79</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>4983.03</v>
+        <v>4955.9</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>8224.98</v>
+        <v>8180.19</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>815.02</v>
+        <v>810.58</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>16733.61</v>
+        <v>16642.48</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2520.75</v>
+        <v>2507.03</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>2237.7</v>
+        <v>2225.51</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>4907.64</v>
+        <v>4880.92</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>3618.8</v>
+        <v>3599.09</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4518.8</v>
+        <v>4494.19</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>1810.46</v>
+        <v>1800.6</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>907</v>
+        <v>902.0599999999999</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>6982.78</v>
+        <v>6944.76</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>26053.77</v>
+        <v>25911.89</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>9608.059999999999</v>
+        <v>9555.74</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>1422.89</v>
+        <v>1415.14</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>808.41</v>
+        <v>804</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>953.5</v>
+        <v>948.3</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>6480.61</v>
+        <v>6442.42</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>3039.68</v>
+        <v>3021.76</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>7540.39</v>
+        <v>7495.95</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1651.88</v>
+        <v>1642.15</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2269.82</v>
+        <v>2256.45</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>5662.17</v>
+        <v>5628.8</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>868.28</v>
+        <v>863.16</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>13180.81</v>
+        <v>13103.13</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>17794.4</v>
+        <v>17689.54</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>2585.36</v>
+        <v>2570.12</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>6071.55</v>
+        <v>6035.77</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>856.4400000000001</v>
+        <v>851.39</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>812.05</v>
+        <v>807.27</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>916.09</v>
+        <v>910.6900000000001</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1451.21</v>
+        <v>1442.65</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>3996.1</v>
+        <v>3972.55</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>19050.21</v>
+        <v>18937.94</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>958.47</v>
+        <v>952.8200000000001</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>8625.120000000001</v>
+        <v>8574.290000000001</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>4127.36</v>
+        <v>4103.04</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>3322.44</v>
+        <v>3302.86</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>12200.07</v>
+        <v>12128.18</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1948.13</v>
+        <v>1936.65</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>3222.77</v>
+        <v>3203.78</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>5541.78</v>
+        <v>5509.12</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>4679.63</v>
+        <v>4652.05</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1290.28</v>
+        <v>1282.68</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>4432.54</v>
+        <v>4406.42</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>2318.81</v>
+        <v>2305.15</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>7118.3</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1544.64</v>
+        <v>1535.26</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>3085.74</v>
+        <v>3066.99</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>37025.29</v>
+        <v>36800.31</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>965.67</v>
+        <v>959.8</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>926.02</v>
+        <v>920.4</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1159.93</v>
+        <v>1152.88</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>32932.79</v>
+        <v>32732.68</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>2711.8</v>
+        <v>2695.32</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1734.96</v>
+        <v>1724.42</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>2437.65</v>
+        <v>2422.84</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>11567.1</v>
+        <v>11496.82</v>
       </c>
     </row>
     <row r="626">
@@ -38633,7 +38633,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>812.55</v>
+        <v>807.61</v>
       </c>
     </row>
     <row r="627">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>21484.36</v>
+        <v>21353.81</v>
       </c>
     </row>
     <row r="628">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>1739.98</v>
+        <v>1729.41</v>
       </c>
     </row>
     <row r="629">
@@ -38816,7 +38816,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>9255.780000000001</v>
+        <v>9199.530000000001</v>
       </c>
     </row>
     <row r="630">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>811.41</v>
+        <v>806.48</v>
       </c>
     </row>
     <row r="631">
@@ -38938,7 +38938,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>26753.67</v>
+        <v>26591.11</v>
       </c>
     </row>
     <row r="632">
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>1429.62</v>
+        <v>1420.94</v>
       </c>
     </row>
     <row r="633">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2002.01</v>
+        <v>1989.84</v>
       </c>
     </row>
     <row r="634">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>23246.22</v>
+        <v>23104.97</v>
       </c>
     </row>
     <row r="635">
@@ -39182,7 +39182,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>3985.52</v>
+        <v>3961.3</v>
       </c>
     </row>
     <row r="636">
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>4088.01</v>
+        <v>4063.17</v>
       </c>
     </row>
     <row r="637">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>3593.95</v>
+        <v>3572.11</v>
       </c>
     </row>
     <row r="638">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>2299.77</v>
+        <v>2285.79</v>
       </c>
     </row>
     <row r="639">
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>3929.19</v>
+        <v>3905.31</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>6086.88</v>
+        <v>6049.89</v>
       </c>
     </row>
     <row r="641">
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>3308.82</v>
+        <v>3288.71</v>
       </c>
     </row>
     <row r="642">
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2070.7</v>
+        <v>2058.11</v>
       </c>
     </row>
     <row r="643">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>11980.36</v>
+        <v>11907.57</v>
       </c>
     </row>
     <row r="644">
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1550.65</v>
+        <v>1541.23</v>
       </c>
     </row>
     <row r="645">
@@ -39792,7 +39792,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>912.74</v>
+        <v>907.1900000000001</v>
       </c>
     </row>
     <row r="646">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>808</v>
+        <v>803.09</v>
       </c>
     </row>
     <row r="647">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>4112.56</v>
+        <v>4087.57</v>
       </c>
     </row>
     <row r="648">
@@ -39975,7 +39975,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>21507.85</v>
+        <v>21377.16</v>
       </c>
     </row>
     <row r="649">
@@ -40036,7 +40036,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>9974.84</v>
+        <v>9914.23</v>
       </c>
     </row>
     <row r="650">
@@ -40097,7 +40097,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>5506.75</v>
+        <v>5473.29</v>
       </c>
     </row>
     <row r="651">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>4200.47</v>
+        <v>4174.94</v>
       </c>
     </row>
     <row r="652">
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1651.69</v>
+        <v>1641.65</v>
       </c>
     </row>
     <row r="653">
@@ -40280,7 +40280,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1619.61</v>
+        <v>1609.77</v>
       </c>
     </row>
     <row r="654">
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>2233.9</v>
+        <v>2220.32</v>
       </c>
     </row>
     <row r="655">
@@ -40402,7 +40402,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>922.46</v>
+        <v>918.9</v>
       </c>
     </row>
     <row r="656">
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1888.15</v>
+        <v>1880.86</v>
       </c>
     </row>
     <row r="657">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>8029.1</v>
+        <v>7998.11</v>
       </c>
     </row>
     <row r="658">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>79520.86</v>
+        <v>79213.94</v>
       </c>
     </row>
     <row r="659">
@@ -40646,7 +40646,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>56710.14</v>
+        <v>56491.25</v>
       </c>
     </row>
     <row r="660">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>815.86</v>
+        <v>812.71</v>
       </c>
     </row>
     <row r="661">
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>864.63</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="662">
@@ -40829,7 +40829,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>2428.3</v>
+        <v>2418.92</v>
       </c>
     </row>
     <row r="663">
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>3845.74</v>
+        <v>3830.89</v>
       </c>
     </row>
     <row r="664">
@@ -40951,7 +40951,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>2132.84</v>
+        <v>2124.61</v>
       </c>
     </row>
     <row r="665">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>6889.14</v>
+        <v>6862.55</v>
       </c>
     </row>
     <row r="666">
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>2072.88</v>
+        <v>2064.88</v>
       </c>
     </row>
     <row r="667">
@@ -41134,7 +41134,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>3363.4</v>
+        <v>3350.42</v>
       </c>
     </row>
     <row r="668">
@@ -41195,7 +41195,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>1289.85</v>
+        <v>1284.87</v>
       </c>
     </row>
     <row r="669">
@@ -41256,7 +41256,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>33522.68</v>
+        <v>33393.3</v>
       </c>
     </row>
     <row r="670">
@@ -41317,7 +41317,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2124.32</v>
+        <v>2116.12</v>
       </c>
     </row>
     <row r="671">
@@ -41378,7 +41378,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>10717.56</v>
+        <v>10676.2</v>
       </c>
     </row>
     <row r="672">
@@ -41439,7 +41439,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>887.92</v>
+        <v>884.5</v>
       </c>
     </row>
     <row r="673">
@@ -41500,7 +41500,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>12216.04</v>
+        <v>12168.89</v>
       </c>
     </row>
     <row r="674">
@@ -41561,7 +41561,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>4285.84</v>
+        <v>4269.3</v>
       </c>
     </row>
     <row r="675">
@@ -41622,7 +41622,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>839.8200000000001</v>
+        <v>836.58</v>
       </c>
     </row>
     <row r="676">
@@ -41683,7 +41683,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>20355.15</v>
+        <v>20276.59</v>
       </c>
     </row>
     <row r="677">
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>3916.75</v>
+        <v>3901.63</v>
       </c>
     </row>
     <row r="678">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1959.78</v>
+        <v>1952.22</v>
       </c>
     </row>
     <row r="679">
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>807.73</v>
+        <v>804.62</v>
       </c>
     </row>
     <row r="680">
@@ -41927,7 +41927,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>807.9</v>
+        <v>804.78</v>
       </c>
     </row>
     <row r="681">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>7182.22</v>
+        <v>7154.5</v>
       </c>
     </row>
     <row r="682">
@@ -42049,7 +42049,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1647.5</v>
+        <v>1641.15</v>
       </c>
     </row>
     <row r="683">
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>915.5599999999999</v>
+        <v>912.02</v>
       </c>
     </row>
     <row r="684">
@@ -42171,7 +42171,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>3501.72</v>
+        <v>3488.21</v>
       </c>
     </row>
     <row r="685">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>20757.07</v>
+        <v>20676.95</v>
       </c>
     </row>
     <row r="686">
@@ -42293,7 +42293,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>8071.57</v>
+        <v>8040.41</v>
       </c>
     </row>
     <row r="687">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>7150.88</v>
+        <v>7123.28</v>
       </c>
     </row>
     <row r="688">
@@ -42415,7 +42415,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>1091.06</v>
+        <v>1086.85</v>
       </c>
     </row>
     <row r="689">
@@ -42476,7 +42476,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>2182.12</v>
+        <v>2173.7</v>
       </c>
     </row>
     <row r="690">
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>834.91</v>
+        <v>831.6900000000001</v>
       </c>
     </row>
     <row r="691">
@@ -42598,7 +42598,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>1161.38</v>
+        <v>1156.9</v>
       </c>
     </row>
     <row r="692">
@@ -42659,7 +42659,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>5600.1</v>
+        <v>5578.49</v>
       </c>
     </row>
     <row r="693">
@@ -42720,7 +42720,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>823.4</v>
+        <v>820.22</v>
       </c>
     </row>
     <row r="694">
@@ -42781,7 +42781,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>833.1</v>
+        <v>829.89</v>
       </c>
     </row>
     <row r="695">
@@ -42842,7 +42842,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>4207.12</v>
+        <v>4228.9</v>
       </c>
     </row>
     <row r="696">
@@ -42903,7 +42903,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>67873.63</v>
+        <v>68225.03999999999</v>
       </c>
     </row>
     <row r="697">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>6318.61</v>
+        <v>6351.32</v>
       </c>
     </row>
     <row r="698">
@@ -43025,7 +43025,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>1020.92</v>
+        <v>1026.2</v>
       </c>
     </row>
     <row r="699">
@@ -43086,7 +43086,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1840.14</v>
+        <v>1849.66</v>
       </c>
     </row>
     <row r="700">
@@ -43147,7 +43147,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>1792.05</v>
+        <v>1801.33</v>
       </c>
     </row>
     <row r="701">
@@ -43208,7 +43208,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>913.05</v>
+        <v>917.78</v>
       </c>
     </row>
     <row r="702">
@@ -43269,7 +43269,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>4188.89</v>
+        <v>4210.58</v>
       </c>
     </row>
     <row r="703">
@@ -43330,7 +43330,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>9566.99</v>
+        <v>9616.52</v>
       </c>
     </row>
     <row r="704">
@@ -43391,7 +43391,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>6707.86</v>
+        <v>6742.58</v>
       </c>
     </row>
     <row r="705">
@@ -43452,7 +43452,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>1029.52</v>
+        <v>1034.85</v>
       </c>
     </row>
     <row r="706">
@@ -43513,7 +43513,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>905.13</v>
+        <v>909.8099999999999</v>
       </c>
     </row>
     <row r="707">
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>1661.45</v>
+        <v>1670.05</v>
       </c>
     </row>
     <row r="708">
@@ -43635,7 +43635,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>3532.01</v>
+        <v>3550.29</v>
       </c>
     </row>
     <row r="709">
@@ -43696,7 +43696,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3431.81</v>
+        <v>3449.58</v>
       </c>
     </row>
     <row r="710">
@@ -43757,7 +43757,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>6455.41</v>
+        <v>6488.83</v>
       </c>
     </row>
     <row r="711">
@@ -43818,7 +43818,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>12446.87</v>
+        <v>12511.32</v>
       </c>
     </row>
     <row r="712">
@@ -43879,7 +43879,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>10205.05</v>
+        <v>10257.88</v>
       </c>
     </row>
     <row r="713">
@@ -43940,7 +43940,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1199.51</v>
+        <v>1205.72</v>
       </c>
     </row>
     <row r="714">
@@ -44001,7 +44001,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>11663.4</v>
+        <v>11723.79</v>
       </c>
     </row>
     <row r="715">
@@ -44062,7 +44062,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>1202.96</v>
+        <v>1209.19</v>
       </c>
     </row>
     <row r="716">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2419.54</v>
+        <v>2432.06</v>
       </c>
     </row>
     <row r="717">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>2661.08</v>
+        <v>2674.86</v>
       </c>
     </row>
     <row r="718">
@@ -44245,7 +44245,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>843.37</v>
+        <v>847.74</v>
       </c>
     </row>
     <row r="719">
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>14176.21</v>
+        <v>14249.6</v>
       </c>
     </row>
     <row r="720">
@@ -44367,7 +44367,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>3355.88</v>
+        <v>3373.26</v>
       </c>
     </row>
     <row r="721">
@@ -44428,7 +44428,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1029.9</v>
+        <v>1035.23</v>
       </c>
     </row>
     <row r="722">
@@ -44489,7 +44489,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>870.46</v>
+        <v>874.97</v>
       </c>
     </row>
     <row r="723">
@@ -44550,7 +44550,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>16538.61</v>
+        <v>16624.23</v>
       </c>
     </row>
     <row r="724">
@@ -44611,7 +44611,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>1471.41</v>
+        <v>1479.03</v>
       </c>
     </row>
     <row r="725">
@@ -44672,7 +44672,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>5173.48</v>
+        <v>5200.27</v>
       </c>
     </row>
     <row r="726">
@@ -44733,7 +44733,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>1140.88</v>
+        <v>1146.78</v>
       </c>
     </row>
     <row r="727">
@@ -44794,7 +44794,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>814.5</v>
+        <v>818.71</v>
       </c>
     </row>
     <row r="728">
@@ -44855,7 +44855,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>1512.4</v>
+        <v>1520.23</v>
       </c>
     </row>
     <row r="729">
@@ -44916,7 +44916,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>5174</v>
+        <v>5200.79</v>
       </c>
     </row>
     <row r="730">
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>1076.46</v>
+        <v>1082.03</v>
       </c>
     </row>
     <row r="731">
@@ -45038,7 +45038,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>868.24</v>
+        <v>872.74</v>
       </c>
     </row>
     <row r="732">
@@ -45099,7 +45099,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>1055.86</v>
+        <v>1061.33</v>
       </c>
     </row>
     <row r="733">
@@ -45160,7 +45160,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>3472.23</v>
+        <v>3475.58</v>
       </c>
     </row>
     <row r="734">
@@ -45221,7 +45221,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>6430.82</v>
+        <v>6437.02</v>
       </c>
     </row>
     <row r="735">
@@ -45282,7 +45282,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>5392.34</v>
+        <v>5397.54</v>
       </c>
     </row>
     <row r="736">
@@ -45343,7 +45343,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>2314.43</v>
+        <v>2316.66</v>
       </c>
     </row>
     <row r="737">
@@ -45404,7 +45404,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>4909.19</v>
+        <v>4913.92</v>
       </c>
     </row>
     <row r="738">
@@ -45465,7 +45465,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>1831.94</v>
+        <v>1833.71</v>
       </c>
     </row>
     <row r="739">
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>2022.18</v>
+        <v>2024.13</v>
       </c>
     </row>
     <row r="740">
@@ -45587,7 +45587,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>2549.99</v>
+        <v>2552.45</v>
       </c>
     </row>
     <row r="741">
@@ -45648,7 +45648,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>849.62</v>
+        <v>850.4299999999999</v>
       </c>
     </row>
     <row r="742">
@@ -45709,7 +45709,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>3177.9</v>
+        <v>3180.97</v>
       </c>
     </row>
     <row r="743">
@@ -45770,7 +45770,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>33344.02</v>
+        <v>33376.16</v>
       </c>
     </row>
     <row r="744">
@@ -45831,7 +45831,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>2900.78</v>
+        <v>2903.58</v>
       </c>
     </row>
     <row r="745">
@@ -45892,7 +45892,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2880.82</v>
+        <v>2883.6</v>
       </c>
     </row>
     <row r="746">
@@ -45953,7 +45953,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2137.81</v>
+        <v>2139.87</v>
       </c>
     </row>
     <row r="747">
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>9124.139999999999</v>
+        <v>9132.93</v>
       </c>
     </row>
     <row r="748">
@@ -46075,7 +46075,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>10788.78</v>
+        <v>10799.18</v>
       </c>
     </row>
     <row r="749">
@@ -46136,7 +46136,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>825.66</v>
+        <v>826.46</v>
       </c>
     </row>
     <row r="750">
@@ -46197,7 +46197,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>5708.04</v>
+        <v>5713.54</v>
       </c>
     </row>
     <row r="751">
@@ -46258,7 +46258,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>3154.67</v>
+        <v>3157.71</v>
       </c>
     </row>
     <row r="752">
@@ -46319,7 +46319,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>824.64</v>
+        <v>825.4299999999999</v>
       </c>
     </row>
     <row r="753">
@@ -46380,7 +46380,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>2686.71</v>
+        <v>2689.29</v>
       </c>
     </row>
     <row r="754">
@@ -46441,7 +46441,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>3220.93</v>
+        <v>3224.04</v>
       </c>
     </row>
     <row r="755">
@@ -46502,7 +46502,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>8908.450000000001</v>
+        <v>8917.040000000001</v>
       </c>
     </row>
     <row r="756">
@@ -46563,7 +46563,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>990.16</v>
+        <v>991.12</v>
       </c>
     </row>
     <row r="757">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>3156.84</v>
+        <v>3159.88</v>
       </c>
     </row>
     <row r="758">
@@ -46685,7 +46685,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>3863.44</v>
+        <v>3867.16</v>
       </c>
     </row>
     <row r="759">
@@ -46746,7 +46746,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>1599.26</v>
+        <v>1600.8</v>
       </c>
     </row>
     <row r="760">
@@ -46807,7 +46807,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>1523</v>
+        <v>1524.47</v>
       </c>
     </row>
     <row r="761">
@@ -46868,7 +46868,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>71833.03999999999</v>
+        <v>71902.27</v>
       </c>
     </row>
     <row r="762">
@@ -46929,7 +46929,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>12442.45</v>
+        <v>12454.44</v>
       </c>
     </row>
     <row r="763">
@@ -46990,7 +46990,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>1494.65</v>
+        <v>1496.09</v>
       </c>
     </row>
     <row r="764">
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>3644.44</v>
+        <v>3647.95</v>
       </c>
     </row>
     <row r="765">
@@ -47112,7 +47112,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>27155.18</v>
+        <v>27181.36</v>
       </c>
     </row>
     <row r="766">
@@ -47173,7 +47173,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>7306.82</v>
+        <v>7313.86</v>
       </c>
     </row>
     <row r="767">
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>5389.84</v>
+        <v>5395.04</v>
       </c>
     </row>
     <row r="768">
@@ -47295,7 +47295,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>1379.11</v>
+        <v>1380.44</v>
       </c>
     </row>
     <row r="769">
@@ -47356,7 +47356,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>2415.8</v>
+        <v>2418.13</v>
       </c>
     </row>
     <row r="770">
@@ -47417,7 +47417,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>2678.25</v>
+        <v>2680.83</v>
       </c>
     </row>
     <row r="771">
@@ -47478,7 +47478,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>4488.85</v>
+        <v>4493.18</v>
       </c>
     </row>
     <row r="772">
@@ -47539,7 +47539,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>890.63</v>
+        <v>891.49</v>
       </c>
     </row>
     <row r="773">
@@ -47600,7 +47600,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>1790.48</v>
+        <v>1792.21</v>
       </c>
     </row>
     <row r="774">
@@ -47661,7 +47661,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>821.65</v>
+        <v>822.4400000000001</v>
       </c>
     </row>
     <row r="775">
@@ -47722,7 +47722,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>1362.94</v>
+        <v>1364.25</v>
       </c>
     </row>
     <row r="776">
@@ -47783,7 +47783,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>3842.63</v>
+        <v>3846.33</v>
       </c>
     </row>
     <row r="777">
@@ -47844,7 +47844,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>1621.73</v>
+        <v>1623.3</v>
       </c>
     </row>
     <row r="778">
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>3269.7</v>
+        <v>3272.86</v>
       </c>
     </row>
     <row r="779">
@@ -47966,7 +47966,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>11226.58</v>
+        <v>11237.39</v>
       </c>
     </row>
     <row r="780">
@@ -48027,7 +48027,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>1146.99</v>
+        <v>1148.1</v>
       </c>
     </row>
     <row r="781">
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>1679.77</v>
+        <v>1681.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43310,7 +43310,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44164,7 +44164,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44225,7 +44225,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44408,7 +44408,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -45262,7 +45262,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46116,7 +46116,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46604,7 +46604,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46726,7 +46726,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46848,7 +46848,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -47275,7 +47275,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47397,7 +47397,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47824,7 +47824,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Angol</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE MARINA HOSP NAVAL ALMIR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dirección de Planificación de Inf. del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL  E INMOB MAS COMERCIO LTDA.</t>
+          <t>Sociedad Comercial  e Inmob Mas Comercio Ltda.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE PETORCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL XIV REGION DE LOS RIOS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Serplac IX Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE TALCAHUANO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Juzgado de Familia de Rengo</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -24944,7 +24944,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25249,7 +25249,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Pinto Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Femenino Semiabierto St</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. de la División Logística</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30861,7 +30861,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -31105,7 +31105,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cochamó - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31776,7 +31776,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32213,7 +32213,7 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
@@ -32325,7 +32325,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -33118,7 +33118,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>ESCUELA DE FORMACIÓN DE CARABINEROS LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33179,7 +33179,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33545,12 +33545,12 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -34216,7 +34216,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -34277,7 +34277,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>I Municipalidad de Lago Ranco</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34460,7 +34460,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34521,7 +34521,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34948,7 +34948,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -35182,7 +35182,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -35741,7 +35741,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -36046,7 +36046,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -36107,7 +36107,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36168,7 +36168,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36473,7 +36473,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -36656,7 +36656,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -36839,7 +36839,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Juzgado de Familia de Los Andes</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -37083,7 +37083,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -37398,7 +37398,7 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
@@ -37632,7 +37632,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37815,7 +37815,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN-SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -38242,7 +38242,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>gerencia</t>
+          <t>Corporación Municipal de Cultura de San Clemente</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -38669,7 +38669,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DEL ACONCAGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38730,7 +38730,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -39035,7 +39035,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39401,7 +39401,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -39594,7 +39594,7 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
@@ -39828,7 +39828,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial Región  Biobío</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -39889,7 +39889,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -40255,7 +40255,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -40560,7 +40560,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -40621,7 +40621,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -41170,7 +41170,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -41353,7 +41353,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -41414,7 +41414,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -41536,7 +41536,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -41597,7 +41597,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41963,7 +41963,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -42085,7 +42085,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>DIVISIÓN DE BIENESTAR SOCIAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -42146,7 +42146,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -42156,7 +42156,7 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
@@ -42268,7 +42268,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42329,7 +42329,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -42390,7 +42390,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -42451,7 +42451,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42634,7 +42634,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>DIVISION DE SALUD</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -42695,7 +42695,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERPLAC VII REGION								</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42939,7 +42939,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -43066,7 +43066,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43122,7 +43122,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -43671,7 +43671,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -43732,7 +43732,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -45318,7 +45318,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45440,7 +45440,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -45750,7 +45750,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45867,7 +45867,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -45989,7 +45989,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46843,7 +46843,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -46965,7 +46965,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -47392,7 +47392,7 @@
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47575,7 +47575,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -47636,7 +47636,7 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -47697,7 +47697,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar La Reina</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2801,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2988,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3244,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3439,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3504,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3569,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3634,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3760,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3825,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3890,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3955,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4020,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4150,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4337,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4532,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4723,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4788,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4979,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5044,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5109,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5174,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5239,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5365,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5430,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5495,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5560,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5625,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5755,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5881,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5946,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6011,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6076,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6324,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6389,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6519,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6714,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6779,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6905,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7031,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7157,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7222,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7409,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7730,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7795,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7860,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7925,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7990,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8055,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8120,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8368,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8433,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8498,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8563,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8628,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8693,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8758,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8884,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9144,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9209,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9274,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9400,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9465,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9660,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9725,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9851,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9977,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10103,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10229,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10294,11 @@
           <t>77.947.545-K</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10359,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10424,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10489,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10554,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10619,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10684,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10749,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10814,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10944,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11009,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11074,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11269,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11334,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11785,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11976,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12041,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12106,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12171,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12236,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12301,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12561,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12626,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12691,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12756,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12882,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12947,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13012,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13077,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13207,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13337,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13402,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13528,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13654,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13910,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13975,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14101,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14227,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14292,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14418,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14483,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14670,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14800,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15052,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15178,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15365,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15430,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15556,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15621,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15686,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15877,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15942,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16007,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16198,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16263,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16328,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16393,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16458,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16523,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16718,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16848,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16913,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17043,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17108,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17234,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17299,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17364,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17429,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17494,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17807,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17872,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17937,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18002,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18067,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18132,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18197,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18262,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18327,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18457,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18522,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18587,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18652,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18839,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18904,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18969,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19099,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19164,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19229,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19294,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19359,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19550,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19680,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19806,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19871,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19936,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20001,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20066,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20387,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20452,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20517,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20582,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20647,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20777,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20842,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20907,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20972,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21037,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21232,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21358,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21423,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21549,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21614,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21679,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21805,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21931,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21996,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22061,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22191,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22256,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22386,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22577,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23862,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24053,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24569,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24634,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24699,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24825,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25016,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25337,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25402,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25467,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25532,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25597,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25723,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25849,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25914,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26040,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26170,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26235,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26300,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26491,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26556,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26621,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26686,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26751,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26816,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26881,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26946,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27011,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27076,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27263,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27328,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27393,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27649,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27714,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27779,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27905,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28031,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28096,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28161,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28226,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28421,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28486,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28551,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28616,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28811,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28876,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28941,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29071,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29197,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29262,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29392,11 @@
           <t>76.559.762-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29518,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29583,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29648,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29774,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29904,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29969,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30095,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30286,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30351,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30416,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30481,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30607,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30672,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30737,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30863,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30928,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30993,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31180,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31245,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31432,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31562,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31814,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32005,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32200,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32265,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32395,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32647,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32712,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32842,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32972,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33037,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33102,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33167,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33232,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33484,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33549,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33675,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33866,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33931,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34061,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34126,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34252,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34317,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34382,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34447,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34512,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34577,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34642,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34707,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34772,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34837,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +35028,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35093,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35223,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35288,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35353,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35479,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35605,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35670,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35735,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35800,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35865,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35930,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35995,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +36121,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +36186,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36251,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36316,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36381,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36446,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36572,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36637,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35027,7 +36763,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36889,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36954,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35332,7 +37080,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37328,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37393,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37523,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35820,7 +37588,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37653,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35942,7 +37718,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37783,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37848,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37913,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37978,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +38043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +38108,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +38173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +38425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38490,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38555,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38746,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38811,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38876,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38941,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +39006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +39132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +39197,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39323,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39388,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39453,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39518,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39583,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39648,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37833,7 +39713,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39778,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37955,7 +39843,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39908,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39973,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +40038,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +40103,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38260,7 +40168,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +40233,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38382,7 +40298,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38443,7 +40363,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40428,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +40493,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +40558,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +40623,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +40814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38931,7 +40879,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +40944,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +41009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +41074,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +41139,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39236,7 +41204,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +41330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41460,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41712,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41777,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39846,7 +41842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +41907,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +42033,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +42098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +42163,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +42228,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40273,7 +42293,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +42358,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +42423,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40456,7 +42488,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42553,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42618,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42683,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42748,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +42813,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42878,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42943,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +43008,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +43073,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41066,7 +43138,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +43203,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +43329,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +43394,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41371,7 +43459,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41432,7 +43524,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41493,7 +43589,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +43654,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41676,7 +43784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41798,7 +43914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43979,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41981,7 +44105,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42042,7 +44170,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42103,7 +44235,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42225,7 +44361,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +44426,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +44491,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44556,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42469,7 +44621,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +44747,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42652,7 +44812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +44877,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +44942,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +45007,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42896,7 +45072,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43018,7 +45198,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43140,7 +45324,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43201,7 +45389,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43323,7 +45515,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43384,7 +45580,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43445,7 +45645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43506,7 +45710,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +45775,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43628,7 +45840,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43750,7 +45966,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43811,7 +46031,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43872,7 +46096,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +46161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +46226,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +46291,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44177,7 +46417,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44238,7 +46482,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44299,7 +46547,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44360,7 +46612,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +46677,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44482,7 +46742,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44543,7 +46807,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44665,7 +46933,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44726,7 +46998,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44848,7 +47124,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44909,7 +47189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44970,7 +47254,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45092,7 +47380,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45153,7 +47445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45275,7 +47571,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45397,7 +47697,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45580,7 +47884,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45641,7 +47949,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45702,7 +48014,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45763,7 +48079,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45824,7 +48144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45946,7 +48270,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46007,7 +48335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46068,7 +48400,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46129,7 +48465,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46190,7 +48530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46251,7 +48595,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46312,7 +48660,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46373,7 +48725,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46434,7 +48790,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46495,7 +48855,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +48920,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46617,7 +48985,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46678,7 +49050,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46739,7 +49115,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46861,7 +49241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46922,7 +49306,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +49371,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47105,7 +49497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +49745,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47410,7 +49810,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +49875,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47532,7 +49940,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47593,7 +50005,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47654,7 +50070,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47715,7 +50135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47898,7 +50322,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48020,7 +50448,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48081,7 +50513,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
